--- a/Output/results13:08.xlsx
+++ b/Output/results13:08.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charliebrown/code/GitHub/carbamylation/Output/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charliebrown/code/GitHub/carbamylation/Output/results13:"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3578077D-59D5-C14C-B16F-010048225809}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7E12F6-ECFA-3C40-9C5F-F071ACA4FF5B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="27640" windowHeight="16440"/>
+    <workbookView xWindow="2640" yWindow="500" windowWidth="20100" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -311,7 +311,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,6 +491,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -652,8 +658,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1008,7 +1015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J544"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1138,34 +1145,34 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>122</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>7.0449999999999999</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>7.7781745930519799E-2</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>26.4731540679931</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>6.7294855117797798</v>
       </c>
     </row>
@@ -1522,34 +1529,34 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>122</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>6.9349999999999996</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>0.24748737341529201</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>24.194452285766602</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>1.4217231273651101</v>
       </c>
     </row>
@@ -1906,34 +1913,34 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>122</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>6.72</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29" t="s">
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>23.2561645507812</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>2.9382262229919398</v>
       </c>
     </row>
@@ -2226,34 +2233,34 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>122</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1">
         <v>6.83</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="1">
         <v>2.8284271247461901E-2</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="1">
         <v>20.642356872558501</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="1">
         <v>3.0330071449279701</v>
       </c>
     </row>
@@ -2546,34 +2553,34 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49">
+      <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="1">
         <v>169</v>
       </c>
-      <c r="C49" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="C49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="1">
         <v>-1.84</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="1">
         <v>4.2426406871192798E-2</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2738,34 +2745,34 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A55">
+      <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="1">
         <v>169</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="D55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="1">
         <v>-3.4049999999999998</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="1">
         <v>0.38890872965260098</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
+      <c r="I55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3218,34 +3225,34 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A70">
+      <c r="A70" s="1">
         <v>68</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="1">
         <v>204</v>
       </c>
-      <c r="C70" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="C70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1">
         <v>8.9499999999999993</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3826,34 +3833,34 @@
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A89">
+      <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="1">
         <v>204</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D89" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="D89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="1">
         <v>8.9600000000000009</v>
       </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-      <c r="H89" t="s">
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
+      <c r="I89" s="1">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4434,34 +4441,34 @@
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A108">
+      <c r="A108" s="1">
         <v>106</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="1">
         <v>204</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D108" t="s">
-        <v>10</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="D108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F108">
+      <c r="F108" s="1">
         <v>8.9499999999999993</v>
       </c>
-      <c r="G108">
-        <v>0</v>
-      </c>
-      <c r="H108" t="s">
+      <c r="G108" s="1">
+        <v>0</v>
+      </c>
+      <c r="H108" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I108">
-        <v>0</v>
-      </c>
-      <c r="J108">
+      <c r="I108" s="1">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5394,34 +5401,34 @@
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A138">
+      <c r="A138" s="1">
         <v>136</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="1">
         <v>129</v>
       </c>
-      <c r="C138" t="s">
-        <v>9</v>
-      </c>
-      <c r="D138" t="s">
-        <v>10</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="C138" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F138">
+      <c r="F138" s="1">
         <v>6.3849999999999998</v>
       </c>
-      <c r="G138">
+      <c r="G138" s="1">
         <v>0.38890872965260098</v>
       </c>
-      <c r="H138" t="s">
+      <c r="H138" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I138">
+      <c r="I138" s="1">
         <v>11.3935089111328</v>
       </c>
-      <c r="J138">
+      <c r="J138" s="1">
         <v>5.8764533996581996</v>
       </c>
     </row>
@@ -5810,34 +5817,34 @@
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A151">
+      <c r="A151" s="1">
         <v>149</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="1">
         <v>129</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D151" t="s">
-        <v>10</v>
-      </c>
-      <c r="E151" t="s">
+      <c r="D151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F151">
+      <c r="F151" s="1">
         <v>5.9550000000000001</v>
       </c>
-      <c r="G151">
+      <c r="G151" s="1">
         <v>0.346482322781408</v>
       </c>
-      <c r="H151" t="s">
+      <c r="H151" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I151">
+      <c r="I151" s="1">
         <v>7.0371675491332999</v>
       </c>
-      <c r="J151">
+      <c r="J151" s="1">
         <v>9.4781182706355993E-2</v>
       </c>
     </row>
@@ -6290,34 +6297,34 @@
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A166">
+      <c r="A166" s="1">
         <v>164</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="1">
         <v>70</v>
       </c>
-      <c r="C166" t="s">
-        <v>9</v>
-      </c>
-      <c r="D166" t="s">
-        <v>10</v>
-      </c>
-      <c r="E166" t="s">
+      <c r="C166" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F166">
+      <c r="F166" s="1">
         <v>6.8433333333333302</v>
       </c>
-      <c r="G166">
+      <c r="G166" s="1">
         <v>5.5075705472860802E-2</v>
       </c>
-      <c r="H166" t="s">
+      <c r="H166" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I166">
-        <v>0</v>
-      </c>
-      <c r="J166">
+      <c r="I166" s="1">
+        <v>0</v>
+      </c>
+      <c r="J166" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6962,34 +6969,34 @@
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A187">
+      <c r="A187" s="1">
         <v>185</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="1">
         <v>70</v>
       </c>
-      <c r="C187" t="s">
+      <c r="C187" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D187" t="s">
-        <v>10</v>
-      </c>
-      <c r="E187" t="s">
+      <c r="D187" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F187">
+      <c r="F187" s="1">
         <v>6.94</v>
       </c>
-      <c r="G187">
+      <c r="G187" s="1">
         <v>7.8102496759066706E-2</v>
       </c>
-      <c r="H187" t="s">
+      <c r="H187" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I187">
-        <v>0</v>
-      </c>
-      <c r="J187">
+      <c r="I187" s="1">
+        <v>0</v>
+      </c>
+      <c r="J187" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7634,34 +7641,34 @@
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A208">
+      <c r="A208" s="1">
         <v>206</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="1">
         <v>70</v>
       </c>
-      <c r="C208" t="s">
+      <c r="C208" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D208" t="s">
-        <v>10</v>
-      </c>
-      <c r="E208" t="s">
+      <c r="D208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E208" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F208">
+      <c r="F208" s="1">
         <v>7.3250000000000002</v>
       </c>
-      <c r="G208">
+      <c r="G208" s="1">
         <v>0.17677669529663601</v>
       </c>
-      <c r="H208" t="s">
+      <c r="H208" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I208">
+      <c r="I208" s="1">
         <v>9.0477867126464808</v>
       </c>
-      <c r="J208">
+      <c r="J208" s="1">
         <v>0.66347098350524902</v>
       </c>
     </row>
@@ -8242,34 +8249,34 @@
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A227">
+      <c r="A227" s="1">
         <v>225</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="1">
         <v>70</v>
       </c>
-      <c r="C227" t="s">
+      <c r="C227" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D227" t="s">
-        <v>10</v>
-      </c>
-      <c r="E227" t="s">
+      <c r="D227" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E227" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F227">
+      <c r="F227" s="1">
         <v>7.15</v>
       </c>
-      <c r="G227">
+      <c r="G227" s="1">
         <v>0.38183766184073498</v>
       </c>
-      <c r="H227" t="s">
+      <c r="H227" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I227">
+      <c r="I227" s="1">
         <v>9.9190559387206996</v>
       </c>
-      <c r="J227">
+      <c r="J227" s="1">
         <v>0.56868910789489702</v>
       </c>
     </row>
@@ -9426,34 +9433,34 @@
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A264">
+      <c r="A264" s="1">
         <v>262</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="1">
         <v>219</v>
       </c>
-      <c r="C264" t="s">
-        <v>9</v>
-      </c>
-      <c r="D264" t="s">
-        <v>10</v>
-      </c>
-      <c r="E264" t="s">
+      <c r="C264" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E264" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F264">
+      <c r="F264" s="1">
         <v>10.795</v>
       </c>
-      <c r="G264">
+      <c r="G264" s="1">
         <v>0.65760930650348903</v>
       </c>
-      <c r="H264" t="s">
+      <c r="H264" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I264">
+      <c r="I264" s="1">
         <v>26.205070495605401</v>
       </c>
-      <c r="J264">
+      <c r="J264" s="1">
         <v>5.2129826545715297</v>
       </c>
     </row>
@@ -10034,34 +10041,34 @@
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A283">
+      <c r="A283" s="1">
         <v>281</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="1">
         <v>219</v>
       </c>
-      <c r="C283" t="s">
+      <c r="C283" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D283" t="s">
-        <v>10</v>
-      </c>
-      <c r="E283" t="s">
+      <c r="D283" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E283" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="1">
         <v>0.19</v>
       </c>
-      <c r="G283">
+      <c r="G283" s="1">
         <v>1.3010764773832399</v>
       </c>
-      <c r="H283" t="s">
+      <c r="H283" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I283">
-        <v>0</v>
-      </c>
-      <c r="J283">
+      <c r="I283" s="1">
+        <v>0</v>
+      </c>
+      <c r="J283" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11250,34 +11257,34 @@
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A321">
+      <c r="A321" s="1">
         <v>319</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="1">
         <v>173</v>
       </c>
-      <c r="C321" t="s">
-        <v>9</v>
-      </c>
-      <c r="D321" t="s">
-        <v>10</v>
-      </c>
-      <c r="E321" t="s">
+      <c r="C321" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E321" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F321">
+      <c r="F321" s="1">
         <v>8.67</v>
       </c>
-      <c r="G321">
-        <v>0</v>
-      </c>
-      <c r="H321" t="s">
+      <c r="G321" s="1">
+        <v>0</v>
+      </c>
+      <c r="H321" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I321">
-        <v>0</v>
-      </c>
-      <c r="J321">
+      <c r="I321" s="1">
+        <v>0</v>
+      </c>
+      <c r="J321" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11954,34 +11961,34 @@
       </c>
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A343">
+      <c r="A343" s="1">
         <v>341</v>
       </c>
-      <c r="B343">
+      <c r="B343" s="1">
         <v>173</v>
       </c>
-      <c r="C343" t="s">
+      <c r="C343" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D343" t="s">
-        <v>10</v>
-      </c>
-      <c r="E343" t="s">
+      <c r="D343" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E343" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F343">
+      <c r="F343" s="1">
         <v>8.66</v>
       </c>
-      <c r="G343">
-        <v>0</v>
-      </c>
-      <c r="H343" t="s">
+      <c r="G343" s="1">
+        <v>0</v>
+      </c>
+      <c r="H343" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I343">
-        <v>0</v>
-      </c>
-      <c r="J343">
+      <c r="I343" s="1">
+        <v>0</v>
+      </c>
+      <c r="J343" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12466,34 +12473,34 @@
       </c>
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A359">
+      <c r="A359" s="1">
         <v>357</v>
       </c>
-      <c r="B359">
+      <c r="B359" s="1">
         <v>184</v>
       </c>
-      <c r="C359" t="s">
-        <v>9</v>
-      </c>
-      <c r="D359" t="s">
-        <v>10</v>
-      </c>
-      <c r="E359" t="s">
+      <c r="C359" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E359" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F359">
+      <c r="F359" s="1">
         <v>8.89</v>
       </c>
-      <c r="G359">
-        <v>0</v>
-      </c>
-      <c r="H359" t="s">
+      <c r="G359" s="1">
+        <v>0</v>
+      </c>
+      <c r="H359" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I359">
+      <c r="I359" s="1">
         <v>16.487077713012599</v>
       </c>
-      <c r="J359">
+      <c r="J359" s="1">
         <v>0</v>
       </c>
     </row>
@@ -13362,34 +13369,34 @@
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A387">
+      <c r="A387" s="1">
         <v>385</v>
       </c>
-      <c r="B387">
+      <c r="B387" s="1">
         <v>225</v>
       </c>
-      <c r="C387" t="s">
-        <v>9</v>
-      </c>
-      <c r="D387" t="s">
-        <v>10</v>
-      </c>
-      <c r="E387" t="s">
+      <c r="C387" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E387" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F387">
+      <c r="F387" s="1">
         <v>9.3224999999999998</v>
       </c>
-      <c r="G387">
+      <c r="G387" s="1">
         <v>0.30026377292862499</v>
       </c>
-      <c r="H387" t="s">
+      <c r="H387" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I387">
+      <c r="I387" s="1">
         <v>10.5892620086669</v>
       </c>
-      <c r="J387">
+      <c r="J387" s="1">
         <v>7.86400938034057</v>
       </c>
     </row>
@@ -13874,34 +13881,34 @@
       </c>
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A403">
+      <c r="A403" s="1">
         <v>401</v>
       </c>
-      <c r="B403">
+      <c r="B403" s="1">
         <v>225</v>
       </c>
-      <c r="C403" t="s">
+      <c r="C403" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D403" t="s">
-        <v>10</v>
-      </c>
-      <c r="E403" t="s">
+      <c r="D403" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E403" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F403">
+      <c r="F403" s="1">
         <v>9.6575000000000006</v>
       </c>
-      <c r="G403">
+      <c r="G403" s="1">
         <v>8.7702147446152498E-2</v>
       </c>
-      <c r="H403" t="s">
+      <c r="H403" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I403">
+      <c r="I403" s="1">
         <v>17.458877563476499</v>
       </c>
-      <c r="J403">
+      <c r="J403" s="1">
         <v>6.8386240005493102</v>
       </c>
     </row>
@@ -14354,34 +14361,34 @@
       </c>
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A418">
+      <c r="A418" s="1">
         <v>416</v>
       </c>
-      <c r="B418">
+      <c r="B418" s="1">
         <v>162</v>
       </c>
-      <c r="C418" t="s">
-        <v>9</v>
-      </c>
-      <c r="D418" t="s">
-        <v>10</v>
-      </c>
-      <c r="E418" t="s">
+      <c r="C418" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E418" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F418">
+      <c r="F418" s="1">
         <v>-0.74</v>
       </c>
-      <c r="G418">
-        <v>0</v>
-      </c>
-      <c r="H418" t="s">
+      <c r="G418" s="1">
+        <v>0</v>
+      </c>
+      <c r="H418" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I418">
-        <v>0</v>
-      </c>
-      <c r="J418">
+      <c r="I418" s="1">
+        <v>0</v>
+      </c>
+      <c r="J418" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14834,34 +14841,34 @@
       </c>
     </row>
     <row r="433" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A433">
+      <c r="A433" s="1">
         <v>431</v>
       </c>
-      <c r="B433">
+      <c r="B433" s="1">
         <v>162</v>
       </c>
-      <c r="C433" t="s">
+      <c r="C433" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D433" t="s">
-        <v>10</v>
-      </c>
-      <c r="E433" t="s">
+      <c r="D433" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E433" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F433">
+      <c r="F433" s="1">
         <v>-0.96</v>
       </c>
-      <c r="G433">
-        <v>0</v>
-      </c>
-      <c r="H433" t="s">
+      <c r="G433" s="1">
+        <v>0</v>
+      </c>
+      <c r="H433" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I433">
-        <v>0</v>
-      </c>
-      <c r="J433">
+      <c r="I433" s="1">
+        <v>0</v>
+      </c>
+      <c r="J433" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15474,34 +15481,34 @@
       </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A453">
+      <c r="A453" s="1">
         <v>451</v>
       </c>
-      <c r="B453">
+      <c r="B453" s="1">
         <v>741</v>
       </c>
-      <c r="C453" t="s">
-        <v>9</v>
-      </c>
-      <c r="D453" t="s">
-        <v>10</v>
-      </c>
-      <c r="E453" t="s">
+      <c r="C453" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D453" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E453" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F453">
+      <c r="F453" s="1">
         <v>4.18</v>
       </c>
-      <c r="G453">
-        <v>0</v>
-      </c>
-      <c r="H453" t="s">
+      <c r="G453" s="1">
+        <v>0</v>
+      </c>
+      <c r="H453" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I453">
-        <v>0</v>
-      </c>
-      <c r="J453">
+      <c r="I453" s="1">
+        <v>0</v>
+      </c>
+      <c r="J453" s="1">
         <v>0</v>
       </c>
     </row>
@@ -16274,34 +16281,34 @@
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A478">
+      <c r="A478" s="1">
         <v>476</v>
       </c>
-      <c r="B478">
+      <c r="B478" s="1">
         <v>741</v>
       </c>
-      <c r="C478" t="s">
+      <c r="C478" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D478" t="s">
-        <v>10</v>
-      </c>
-      <c r="E478" t="s">
+      <c r="D478" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E478" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F478">
+      <c r="F478" s="1">
         <v>4.0599999999999996</v>
       </c>
-      <c r="G478">
-        <v>0</v>
-      </c>
-      <c r="H478" t="s">
+      <c r="G478" s="1">
+        <v>0</v>
+      </c>
+      <c r="H478" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I478">
-        <v>0</v>
-      </c>
-      <c r="J478">
+      <c r="I478" s="1">
+        <v>0</v>
+      </c>
+      <c r="J478" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17074,34 +17081,34 @@
       </c>
     </row>
     <row r="503" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A503">
+      <c r="A503" s="1">
         <v>501</v>
       </c>
-      <c r="B503">
+      <c r="B503" s="1">
         <v>741</v>
       </c>
-      <c r="C503" t="s">
+      <c r="C503" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D503" t="s">
-        <v>10</v>
-      </c>
-      <c r="E503" t="s">
+      <c r="D503" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E503" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F503">
+      <c r="F503" s="1">
         <v>4.1399999999999997</v>
       </c>
-      <c r="G503">
-        <v>0</v>
-      </c>
-      <c r="H503" t="s">
+      <c r="G503" s="1">
+        <v>0</v>
+      </c>
+      <c r="H503" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I503">
-        <v>0</v>
-      </c>
-      <c r="J503">
+      <c r="I503" s="1">
+        <v>0</v>
+      </c>
+      <c r="J503" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17874,34 +17881,34 @@
       </c>
     </row>
     <row r="528" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A528">
+      <c r="A528" s="1">
         <v>526</v>
       </c>
-      <c r="B528">
+      <c r="B528" s="1">
         <v>741</v>
       </c>
-      <c r="C528" t="s">
+      <c r="C528" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D528" t="s">
-        <v>10</v>
-      </c>
-      <c r="E528" t="s">
+      <c r="D528" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E528" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F528">
+      <c r="F528" s="1">
         <v>4.1900000000000004</v>
       </c>
-      <c r="G528">
-        <v>0</v>
-      </c>
-      <c r="H528" t="s">
+      <c r="G528" s="1">
+        <v>0</v>
+      </c>
+      <c r="H528" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I528">
-        <v>0</v>
-      </c>
-      <c r="J528">
+      <c r="I528" s="1">
+        <v>0</v>
+      </c>
+      <c r="J528" s="1">
         <v>0</v>
       </c>
     </row>
